--- a/output/fixed/buahsafe_dataset_gabungan_29082026.xlsx
+++ b/output/fixed/buahsafe_dataset_gabungan_29082026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD32032-8757-411A-B492-215B145CD862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
